--- a/data/daily/2026-07/2026-07-13.xlsx
+++ b/data/daily/2026-07/2026-07-13.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카테고리통계" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="카테고리통계" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/daily/2026-07/2026-07-13.xlsx
+++ b/data/daily/2026-07/2026-07-13.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3입 추가증정 "독일 명품 비타민" 오쏘몰 이뮨 멀티비타민&amp;미네랄 30+3입 - 시그니처 기프트 에디션</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1086,7 +1086,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -1157,7 +1157,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1165,29 +1165,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>코엔자임Q10 6캡슐 6일분</t>
+          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000279&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1195,29 +1195,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rTG 오메가3 30캡슐 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1225,29 +1225,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>녹차 카테킨 6정 6일분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000282&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>바나바잎 추출물 30정 (30일분)</t>
+          <t>rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>루테인 30정 30일분</t>
+          <t>rTG오메가3 6캡슐 6일분</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000269&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1315,22 +1315,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000139&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>푸응 7days 팻버닝 21캡슐</t>
+          <t>유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1375,29 +1375,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1405,22 +1405,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>비타민D 4000IU 30정 30일분</t>
+          <t>하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1529,16 +1529,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1595,16 +1595,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1617,16 +1617,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1705,16 +1705,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>

--- a/data/daily/2026-07/2026-07-13.xlsx
+++ b/data/daily/2026-07/2026-07-13.xlsx
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>뉴트리디데이</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4487367</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
     </row>
@@ -1051,22 +1051,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
+          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>뉴트리디데이</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>30,900원</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/4487367</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1135,29 +1135,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>코엔자임 Q10 30캡슐 30일분</t>
+          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1165,29 +1165,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1195,29 +1195,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>녹차 카테킨 6정 6일분</t>
+          <t>마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1235,19 +1235,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000282&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rTG 오메가3 30캡슐 30일분</t>
+          <t>푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rTG오메가3 6캡슐 6일분</t>
+          <t>rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1295,19 +1295,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000269&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1315,29 +1315,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>다이어트 홀릭 15일분</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>유기농 레몬즙 10포</t>
+          <t>코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1375,29 +1375,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>코엔자임Q10 6캡슐 6일분</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000279&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1405,22 +1405,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1595,16 +1595,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1617,16 +1617,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1705,16 +1705,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>

--- a/data/daily/2026-07/2026-07-13.xlsx
+++ b/data/daily/2026-07/2026-07-13.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="카테고리통계" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카테고리통계" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1447,32 +1448,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>비율(%)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>카카오선물하기</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>다이소몰</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>올리브영</t>
         </is>
@@ -1488,7 +1489,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1507,10 +1508,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1519,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1554,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1576,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1598,7 +1599,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1620,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -1639,10 +1640,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -1651,7 +1652,7 @@
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1661,10 +1662,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1673,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1683,10 +1684,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -1695,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1705,7 +1706,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
         <v>20</v>
@@ -1717,7 +1718,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1727,7 +1728,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C13" t="n">
         <v>100</v>
@@ -1739,8 +1740,322 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>칼로(Kalo)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8,500원</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CJ이너비 슬리밍샷 6병/스타터 6병</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CJ이너비</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>34,010원</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[윤광UP]온리추얼 글로우업 글루타치온 콜라겐 7포 (+1포 증정)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>온리추얼 리셋 브라이언 7포 (+1포 증정) (8일분)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋브라이언/글로우업 3종 택1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[리뷰이벤트/10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 앰플</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>라이필</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15,840원</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균)+철분 헤모케어3종</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>37,050원</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>17,400원</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/daily/2026-07/2026-07-13.xlsx
+++ b/data/daily/2026-07/2026-07-13.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카테고리통계" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="카테고리통계" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,7 +683,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -692,29 +691,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>1입 추가증정 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 + 1입 추가 증정 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -722,22 +721,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1입 추가증정 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 + 1입 추가 증정 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
     </row>
@@ -902,22 +901,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>45,000원</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10848340</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
     </row>
@@ -932,22 +931,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>45,000원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/10848340</t>
         </is>
       </c>
     </row>
@@ -962,29 +961,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+베리오트바 2입 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -992,29 +991,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>편안한 밤 필수템 식물성 멜라토닌 1mg 구미 젤리 멜라메이트 1박스 (20구미) 수험생/직장인 선물</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+베리오트바 2입 증정</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CJ웰케어</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11190137</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1022,22 +1021,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
+          <t>편안한 밤 필수템 식물성 멜라토닌 1mg 구미 젤리 멜라메이트 1박스 (20구미) 수험생/직장인 선물</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>CJ웰케어</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/11190137</t>
         </is>
       </c>
     </row>
@@ -1087,8 +1086,8 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1136,29 +1135,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1166,22 +1165,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1196,22 +1195,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>레몬 비타C 500 10포</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1225,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>마그네슘 30정 30일분</t>
+          <t>마그네슘 10정 10일분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1236,19 +1235,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000270&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1256,12 +1255,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>푸응 7days 팻버닝 21캡슐</t>
+          <t>비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1271,14 +1270,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1286,12 +1285,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rTG 오메가3 30캡슐 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1301,7 +1300,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1315,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>다이어트 홀릭 15일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1346,7 +1345,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>코엔자임 Q10 30캡슐 30일분</t>
+          <t>바나바잎 추출물 30정 (30일분)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1356,19 +1355,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1376,7 +1375,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>코엔자임Q10 6캡슐 6일분</t>
+          <t>마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1386,19 +1385,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000279&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1406,12 +1405,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>눈건강엔 루테인지아잔틴</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1421,7 +1420,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1448,32 +1447,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>비율(%)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>카카오선물하기</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>다이소몰</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>올리브영</t>
         </is>
@@ -1489,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1508,10 +1507,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1520,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1530,16 +1529,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1552,16 +1551,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5</v>
+        <v>6.7</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1577,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1596,16 +1595,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1621,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -1640,10 +1639,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>33.3</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -1652,7 +1651,7 @@
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1662,10 +1661,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1674,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1684,10 +1683,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -1696,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1706,7 +1705,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
         <v>20</v>
@@ -1718,7 +1717,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1728,7 +1727,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
         <v>100</v>
@@ -1740,322 +1739,8 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>상품명</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>가격</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>상품URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>칼로(Kalo)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>8,500원</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CJ이너비 슬리밍샷 6병/스타터 6병</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CJ이너비</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>9,900원</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>34,010원</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[윤광UP]온리추얼 글로우업 글루타치온 콜라겐 7포 (+1포 증정)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>온리추얼</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>온리추얼 리셋 브라이언 7포 (+1포 증정) (8일분)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>온리추얼</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋브라이언/글로우업 3종 택1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>온리추얼</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[리뷰이벤트/10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 앰플</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>라이필</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>15,840원</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균)+철분 헤모케어3종</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>37,050원</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>17,400원</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>42,900원</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/daily/2026-07/2026-07-13.xlsx
+++ b/data/daily/2026-07/2026-07-13.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="카테고리통계" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카테고리통계" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -683,7 +684,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -691,29 +692,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1입 추가증정 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 + 1입 추가 증정 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -721,22 +722,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>1입 추가증정 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 + 1입 추가 증정 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
     </row>
@@ -901,22 +902,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>45,000원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/10848340</t>
         </is>
       </c>
     </row>
@@ -931,22 +932,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>45,000원</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10848340</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
     </row>
@@ -961,29 +962,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+베리오트바 2입 증정</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -991,29 +992,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+베리오트바 2입 증정</t>
+          <t>편안한 밤 필수템 식물성 멜라토닌 1mg 구미 젤리 멜라메이트 1박스 (20구미) 수험생/직장인 선물</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>CJ웰케어</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/11190137</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1021,22 +1022,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>편안한 밤 필수템 식물성 멜라토닌 1mg 구미 젤리 멜라메이트 1박스 (20구미) 수험생/직장인 선물</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CJ웰케어</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11190137</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
     </row>
@@ -1086,8 +1087,8 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1135,29 +1136,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>콜린 미오이노시톨 4000 10포</t>
+          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1165,22 +1166,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>멜라드림 30정 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1195,22 +1196,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>레몬 비타C 500 10포</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1226,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>마그네슘 10정 10일분</t>
+          <t>마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1235,19 +1236,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000270&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1255,12 +1256,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>비타민D＆아연 하루구미 30일분</t>
+          <t>푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,14 +1271,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1285,12 +1286,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1300,7 +1301,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1315,29 +1316,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>다이어트 홀릭 15일분</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1345,7 +1346,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>바나바잎 추출물 30정 (30일분)</t>
+          <t>코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1355,19 +1356,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1375,7 +1376,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>마그네슘 30정 30일분</t>
+          <t>코엔자임Q10 6캡슐 6일분</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1385,19 +1386,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000279&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1405,12 +1406,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>눈건강엔 루테인지아잔틴</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1420,7 +1421,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1447,32 +1448,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>비율(%)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>카카오선물하기</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>다이소몰</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>올리브영</t>
         </is>
@@ -1488,7 +1489,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1507,10 +1508,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1519,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1529,16 +1530,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1551,16 +1552,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>6.7</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1576,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1595,16 +1596,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1620,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -1639,10 +1640,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -1651,7 +1652,7 @@
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1661,10 +1662,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1673,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1683,10 +1684,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -1695,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1705,7 +1706,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
         <v>20</v>
@@ -1717,7 +1718,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1727,7 +1728,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C13" t="n">
         <v>100</v>
@@ -1739,8 +1740,322 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>칼로(Kalo)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8,500원</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CJ이너비 슬리밍샷 6병/스타터 6병</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CJ이너비</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>34,010원</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[윤광UP]온리추얼 글로우업 글루타치온 콜라겐 7포 (+1포 증정)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>온리추얼 리셋 브라이언 7포 (+1포 증정) (8일분)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋브라이언/글로우업 3종 택1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[리뷰이벤트/10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 앰플</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>라이필</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15,840원</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균)+철분 헤모케어3종</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>37,050원</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>17,400원</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
